--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Fixed Maturity Plan - Series 85 - 10 Years Plan I.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Fixed Maturity Plan - Series 85 - 10 Years Plan I.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB833EEC-0CCD-4DBD-9A25-5EE02EAE65AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CA835F-8E45-4E55-A1C9-554F156EF6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Fixed Maturity Plan - Series 85 - 10 Years Plan I</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -121,12 +121,12 @@
     <t>IN1920180206</t>
   </si>
   <si>
+    <t>IN2920180311</t>
+  </si>
+  <si>
     <t>IN3320180182</t>
   </si>
   <si>
-    <t>IN2920180311</t>
-  </si>
-  <si>
     <t>State Government of Gujarat</t>
   </si>
   <si>
@@ -259,7 +259,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1084,10 +1084,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="13">
-        <v>43076.430000000008</v>
+        <v>44097.819999999992</v>
       </c>
       <c r="H5" s="14">
-        <v>0.96698555049500012</v>
+        <v>0.94369272306999985</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>13</v>
@@ -1121,10 +1121,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="13">
-        <v>43076.430000000008</v>
+        <v>44097.819999999992</v>
       </c>
       <c r="H7" s="14">
-        <v>0.96698555049500012</v>
+        <v>0.94369272306999985</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>13</v>
@@ -1158,10 +1158,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="13">
-        <v>43076.430000000008</v>
+        <v>44097.819999999992</v>
       </c>
       <c r="H9" s="14">
-        <v>0.96698555049500012</v>
+        <v>0.94369272306999985</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>13</v>
@@ -1187,13 +1187,13 @@
         <v>8570000</v>
       </c>
       <c r="G10" s="20">
-        <v>8971.93</v>
+        <v>9191.18</v>
       </c>
       <c r="H10" s="21">
-        <v>0.2014031030441</v>
+        <v>0.19669112174789999</v>
       </c>
       <c r="I10" s="20">
-        <v>7.19</v>
+        <v>6.31</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>13</v>
@@ -1216,13 +1216,13 @@
         <v>8000000</v>
       </c>
       <c r="G11" s="20">
-        <v>8392.5</v>
+        <v>8589.66</v>
       </c>
       <c r="H11" s="21">
-        <v>0.18839597971649999</v>
+        <v>0.18381860227230001</v>
       </c>
       <c r="I11" s="20">
-        <v>7.16</v>
+        <v>6.31</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>13</v>
@@ -1245,13 +1245,13 @@
         <v>6500000</v>
       </c>
       <c r="G12" s="20">
-        <v>6822.03</v>
+        <v>6976.99</v>
       </c>
       <c r="H12" s="21">
-        <v>0.1531418558838</v>
+        <v>0.14930748712610001</v>
       </c>
       <c r="I12" s="20">
-        <v>7.14</v>
+        <v>6.31</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>13</v>
@@ -1274,13 +1274,13 @@
         <v>3000000</v>
       </c>
       <c r="G13" s="20">
-        <v>3143.78</v>
+        <v>3218.39</v>
       </c>
       <c r="H13" s="21">
-        <v>7.0572000370900001E-2</v>
+        <v>6.8873500390799994E-2</v>
       </c>
       <c r="I13" s="20">
-        <v>7.17</v>
+        <v>6.31</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>13</v>
@@ -1303,13 +1303,13 @@
         <v>1900000</v>
       </c>
       <c r="G14" s="20">
-        <v>1986.89</v>
+        <v>2031.51</v>
       </c>
       <c r="H14" s="21">
-        <v>4.46019765432E-2</v>
+        <v>4.3474285210599997E-2</v>
       </c>
       <c r="I14" s="20">
-        <v>7.15</v>
+        <v>6.31</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>13</v>
@@ -1332,13 +1332,13 @@
         <v>1500000</v>
       </c>
       <c r="G15" s="20">
-        <v>1571.38</v>
+        <v>1608.79</v>
       </c>
       <c r="H15" s="21">
-        <v>3.5274551636199997E-2</v>
+        <v>3.4428083201100003E-2</v>
       </c>
       <c r="I15" s="20">
-        <v>7.19</v>
+        <v>6.33</v>
       </c>
       <c r="J15" s="15" t="s">
         <v>13</v>
@@ -1361,13 +1361,13 @@
         <v>1500000</v>
       </c>
       <c r="G16" s="20">
-        <v>1570.62</v>
+        <v>1608.71</v>
       </c>
       <c r="H16" s="21">
-        <v>3.5257491053000002E-2</v>
+        <v>3.4426371202199997E-2</v>
       </c>
       <c r="I16" s="20">
-        <v>7.15</v>
+        <v>6.27</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>13</v>
@@ -1390,13 +1390,13 @@
         <v>1100000</v>
       </c>
       <c r="G17" s="20">
-        <v>1150.47</v>
+        <v>1178.26</v>
       </c>
       <c r="H17" s="21">
-        <v>2.5825906795800001E-2</v>
+        <v>2.52147473023E-2</v>
       </c>
       <c r="I17" s="20">
-        <v>7.14</v>
+        <v>6.27</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>13</v>
@@ -1404,13 +1404,13 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="16" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="18">
-        <v>8.39</v>
+        <v>8.44</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>18</v>
@@ -1419,13 +1419,13 @@
         <v>1000000</v>
       </c>
       <c r="G18" s="20">
-        <v>1048.32</v>
+        <v>1073.04</v>
       </c>
       <c r="H18" s="21">
-        <v>2.3532829723700001E-2</v>
+        <v>2.2963040793399999E-2</v>
       </c>
       <c r="I18" s="20">
-        <v>7.14</v>
+        <v>6.31</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>13</v>
@@ -1433,13 +1433,13 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="18">
-        <v>8.44</v>
+        <v>8.39</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>18</v>
@@ -1448,13 +1448,13 @@
         <v>1000000</v>
       </c>
       <c r="G19" s="20">
-        <v>1047.9000000000001</v>
+        <v>1072.3900000000001</v>
       </c>
       <c r="H19" s="21">
-        <v>2.3523401506600001E-2</v>
+        <v>2.2949130802699998E-2</v>
       </c>
       <c r="I19" s="20">
-        <v>7.19</v>
+        <v>6.31</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>13</v>
@@ -1477,13 +1477,13 @@
         <v>1000000</v>
       </c>
       <c r="G20" s="20">
-        <v>1047.71</v>
+        <v>1072.3699999999999</v>
       </c>
       <c r="H20" s="21">
-        <v>2.3519136360800001E-2</v>
+        <v>2.2948702802900001E-2</v>
       </c>
       <c r="I20" s="20">
-        <v>7.13</v>
+        <v>6.27</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>13</v>
@@ -1506,13 +1506,13 @@
         <v>990000</v>
       </c>
       <c r="G21" s="20">
-        <v>1039.5</v>
+        <v>1062.8699999999999</v>
       </c>
       <c r="H21" s="21">
-        <v>2.3334837165899999E-2</v>
+        <v>2.2745402937599999E-2</v>
       </c>
       <c r="I21" s="20">
-        <v>7.14</v>
+        <v>6.31</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>13</v>
@@ -1535,13 +1535,13 @@
         <v>900000</v>
       </c>
       <c r="G22" s="20">
-        <v>938.37</v>
+        <v>959.95</v>
       </c>
       <c r="H22" s="21">
-        <v>2.1064657192299999E-2</v>
+        <v>2.0542916396100001E-2</v>
       </c>
       <c r="I22" s="20">
-        <v>7.13</v>
+        <v>6.27</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>13</v>
@@ -1564,13 +1564,13 @@
         <v>518200</v>
       </c>
       <c r="G23" s="20">
-        <v>530.41999999999996</v>
+        <v>543.77</v>
       </c>
       <c r="H23" s="21">
-        <v>1.1906940191900001E-2</v>
+        <v>1.1636670294E-2</v>
       </c>
       <c r="I23" s="20">
-        <v>7.15</v>
+        <v>6.3</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>13</v>
@@ -1593,13 +1593,13 @@
         <v>500000</v>
       </c>
       <c r="G24" s="20">
-        <v>522.65</v>
+        <v>535.24</v>
       </c>
       <c r="H24" s="21">
-        <v>1.1732518176800001E-2</v>
+        <v>1.1454128414800001E-2</v>
       </c>
       <c r="I24" s="20">
-        <v>7.13</v>
+        <v>6.27</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>13</v>
@@ -1622,13 +1622,13 @@
         <v>500000</v>
       </c>
       <c r="G25" s="20">
-        <v>521.95000000000005</v>
+        <v>534.22</v>
       </c>
       <c r="H25" s="21">
-        <v>1.17168044817E-2</v>
+        <v>1.1432300429299999E-2</v>
       </c>
       <c r="I25" s="20">
-        <v>7.13</v>
+        <v>6.27</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>13</v>
@@ -1651,13 +1651,13 @@
         <v>500000</v>
       </c>
       <c r="G26" s="20">
-        <v>501.23</v>
+        <v>515.03</v>
       </c>
       <c r="H26" s="21">
-        <v>1.12516791079E-2</v>
+        <v>1.10216347012E-2</v>
       </c>
       <c r="I26" s="20">
-        <v>7.13</v>
+        <v>6.27</v>
       </c>
       <c r="J26" s="15" t="s">
         <v>13</v>
@@ -1680,13 +1680,13 @@
         <v>500000</v>
       </c>
       <c r="G27" s="20">
-        <v>500.74</v>
+        <v>514.61</v>
       </c>
       <c r="H27" s="21">
-        <v>1.12406795213E-2</v>
+        <v>1.1012646707199999E-2</v>
       </c>
       <c r="I27" s="20">
-        <v>7.12</v>
+        <v>6.25</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>13</v>
@@ -1709,13 +1709,13 @@
         <v>460000</v>
       </c>
       <c r="G28" s="20">
-        <v>480.7</v>
+        <v>491.94</v>
       </c>
       <c r="H28" s="21">
-        <v>1.0790818879900001E-2</v>
+        <v>1.05275090285E-2</v>
       </c>
       <c r="I28" s="20">
-        <v>7.14</v>
+        <v>6.27</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>13</v>
@@ -1738,13 +1738,13 @@
         <v>350000</v>
       </c>
       <c r="G29" s="20">
-        <v>365.55</v>
+        <v>374.09</v>
       </c>
       <c r="H29" s="21">
-        <v>8.2059160422999992E-3</v>
+        <v>8.0055206985999994E-3</v>
       </c>
       <c r="I29" s="20">
-        <v>7.19</v>
+        <v>6.33</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>13</v>
@@ -1767,13 +1767,13 @@
         <v>250000</v>
       </c>
       <c r="G30" s="20">
-        <v>259.67</v>
+        <v>266.02</v>
       </c>
       <c r="H30" s="21">
-        <v>5.8291074235999997E-3</v>
+        <v>5.6928242300999998E-3</v>
       </c>
       <c r="I30" s="20">
-        <v>7.05</v>
+        <v>6.15</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>13</v>
@@ -1796,13 +1796,13 @@
         <v>255300</v>
       </c>
       <c r="G31" s="20">
-        <v>255.76</v>
+        <v>262.60000000000002</v>
       </c>
       <c r="H31" s="21">
-        <v>5.7413352126000003E-3</v>
+        <v>5.6196362784999999E-3</v>
       </c>
       <c r="I31" s="20">
-        <v>7.15</v>
+        <v>6.3</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>13</v>
@@ -1825,13 +1825,13 @@
         <v>200000</v>
       </c>
       <c r="G32" s="20">
-        <v>209.41</v>
+        <v>214.5</v>
       </c>
       <c r="H32" s="21">
-        <v>4.7008641182E-3</v>
+        <v>4.5902969602E-3</v>
       </c>
       <c r="I32" s="20">
-        <v>7.19</v>
+        <v>6.31</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>13</v>
@@ -1854,13 +1854,13 @@
         <v>100000</v>
       </c>
       <c r="G33" s="20">
-        <v>104.48</v>
+        <v>106.99</v>
       </c>
       <c r="H33" s="21">
-        <v>2.3453812284999999E-3</v>
+        <v>2.2895844837000001E-3</v>
       </c>
       <c r="I33" s="20">
-        <v>7.18</v>
+        <v>6.31</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>13</v>
@@ -1883,13 +1883,13 @@
         <v>48300</v>
       </c>
       <c r="G34" s="20">
-        <v>50.56</v>
+        <v>51.77</v>
       </c>
       <c r="H34" s="21">
-        <v>1.1349777461E-3</v>
+        <v>1.1078772663E-3</v>
       </c>
       <c r="I34" s="20">
-        <v>7.13</v>
+        <v>6.27</v>
       </c>
       <c r="J34" s="15" t="s">
         <v>13</v>
@@ -1912,13 +1912,13 @@
         <v>40000</v>
       </c>
       <c r="G35" s="20">
-        <v>41.91</v>
+        <v>42.93</v>
       </c>
       <c r="H35" s="21">
-        <v>9.4080137139999995E-4</v>
+        <v>9.187013916E-4</v>
       </c>
       <c r="I35" s="20">
-        <v>7.19</v>
+        <v>6.31</v>
       </c>
       <c r="J35" s="15" t="s">
         <v>13</v>
@@ -2430,10 +2430,10 @@
         <v>13</v>
       </c>
       <c r="G63" s="13">
-        <v>117.35</v>
+        <v>1790.08</v>
       </c>
       <c r="H63" s="14">
-        <v>2.6342887363E-3</v>
+        <v>3.8307686632000001E-2</v>
       </c>
       <c r="I63" s="13" t="s">
         <v>13</v>
@@ -2467,10 +2467,10 @@
         <v>13</v>
       </c>
       <c r="G65" s="23">
-        <v>1353.3489388899907</v>
+        <v>841.10290731000714</v>
       </c>
       <c r="H65" s="24">
-        <v>3.038016076740933E-2</v>
+        <v>1.7999590296809653E-2</v>
       </c>
       <c r="I65" s="23" t="s">
         <v>13</v>
@@ -2496,10 +2496,10 @@
         <v>13</v>
       </c>
       <c r="G66" s="23">
-        <v>44547.128938889997</v>
+        <v>46729.002907310001</v>
       </c>
       <c r="H66" s="24">
-        <v>0.99999999999870948</v>
+        <v>0.99999999999880951</v>
       </c>
       <c r="I66" s="23" t="s">
         <v>13</v>
